--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务内容表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务内容表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,9 +464,7 @@
           <t>AI计算规划设计与实施服务（训练）</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>套</t>
@@ -477,11 +475,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -499,9 +493,7 @@
           <t>集群系统集成服务</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>10</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>套</t>
@@ -512,11 +504,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -534,9 +522,7 @@
           <t>专项/单次服务</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>次</t>
@@ -547,11 +533,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -569,9 +551,7 @@
           <t>卓悦服务</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>套</t>
@@ -582,11 +562,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -604,9 +580,7 @@
           <t>CCAE</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>480</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>节点</t>
@@ -617,11 +591,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -639,9 +609,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>套</t>
@@ -652,11 +620,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -674,9 +638,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>10</v>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>套</t>
@@ -687,11 +649,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -709,9 +667,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>套</t>
@@ -722,11 +678,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -744,9 +696,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>10</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>套</t>
@@ -757,11 +707,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -779,9 +725,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>套</t>
@@ -792,11 +736,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -814,9 +754,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>套</t>
@@ -827,11 +765,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -849,9 +783,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>10</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>套</t>
@@ -862,11 +794,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -884,9 +812,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>10</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>套</t>
@@ -897,11 +823,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -919,9 +841,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>10</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>套</t>
@@ -932,11 +852,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -954,9 +870,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>10</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>套</t>
@@ -967,11 +881,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -989,9 +899,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>套</t>
@@ -1002,11 +910,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1024,9 +928,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>次</t>
@@ -1037,11 +939,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1059,9 +957,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>次</t>
@@ -1072,11 +968,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1094,9 +986,7 @@
           <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>套</t>
@@ -1107,11 +997,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1129,9 +1015,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>480</v>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1142,11 +1026,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1164,9 +1044,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>480</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1177,11 +1055,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1199,9 +1073,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>480</v>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1212,11 +1084,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1234,9 +1102,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>480</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1247,11 +1113,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -3923,6 +3785,811 @@
       <c r="G116" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>10</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>10</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>480</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>10</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>10</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>10</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>10</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>10</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>10</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>10</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>10</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>10</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>10</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>480</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>480</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>480</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>480</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务内容表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务内容表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,9 +3799,7 @@
           <t>AI计算规划设计与实施服务（训练）</t>
         </is>
       </c>
-      <c r="C117" t="n">
-        <v>10</v>
-      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>套</t>
@@ -3812,11 +3810,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3834,9 +3828,7 @@
           <t>集群系统集成服务</t>
         </is>
       </c>
-      <c r="C118" t="n">
-        <v>10</v>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>套</t>
@@ -3847,11 +3839,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3869,9 +3857,7 @@
           <t>专项/单次服务</t>
         </is>
       </c>
-      <c r="C119" t="n">
-        <v>1</v>
-      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>次</t>
@@ -3882,11 +3868,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3904,9 +3886,7 @@
           <t>卓悦服务</t>
         </is>
       </c>
-      <c r="C120" t="n">
-        <v>1</v>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>套</t>
@@ -3917,11 +3897,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3939,9 +3915,7 @@
           <t>CCAE</t>
         </is>
       </c>
-      <c r="C121" t="n">
-        <v>480</v>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>节点</t>
@@ -3952,11 +3926,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3974,9 +3944,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>10</v>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>套</t>
@@ -3987,11 +3955,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4009,9 +3973,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
         </is>
       </c>
-      <c r="C123" t="n">
-        <v>10</v>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>套</t>
@@ -4022,11 +3984,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4044,9 +4002,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>10</v>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>套</t>
@@ -4057,11 +4013,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4079,9 +4031,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
         </is>
       </c>
-      <c r="C125" t="n">
-        <v>10</v>
-      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>套</t>
@@ -4092,11 +4042,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4114,9 +4060,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
         </is>
       </c>
-      <c r="C126" t="n">
-        <v>10</v>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>套</t>
@@ -4127,11 +4071,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4149,9 +4089,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
         </is>
       </c>
-      <c r="C127" t="n">
-        <v>10</v>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>套</t>
@@ -4162,11 +4100,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4184,9 +4118,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
         </is>
       </c>
-      <c r="C128" t="n">
-        <v>10</v>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>套</t>
@@ -4197,11 +4129,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4219,9 +4147,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
         </is>
       </c>
-      <c r="C129" t="n">
-        <v>10</v>
-      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>套</t>
@@ -4232,11 +4158,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4254,9 +4176,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
         </is>
       </c>
-      <c r="C130" t="n">
-        <v>10</v>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>套</t>
@@ -4267,11 +4187,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4289,9 +4205,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
         </is>
       </c>
-      <c r="C131" t="n">
-        <v>10</v>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>套</t>
@@ -4302,11 +4216,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4324,9 +4234,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
         </is>
       </c>
-      <c r="C132" t="n">
-        <v>10</v>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>套</t>
@@ -4337,11 +4245,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4359,9 +4263,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C133" t="n">
-        <v>1</v>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>次</t>
@@ -4372,11 +4274,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4394,9 +4292,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C134" t="n">
-        <v>1</v>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>次</t>
@@ -4407,11 +4303,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4429,9 +4321,7 @@
           <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
         </is>
       </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>套</t>
@@ -4442,11 +4332,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4464,9 +4350,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
         </is>
       </c>
-      <c r="C136" t="n">
-        <v>480</v>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>节点</t>
@@ -4477,11 +4361,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4499,9 +4379,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
         </is>
       </c>
-      <c r="C137" t="n">
-        <v>480</v>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>节点</t>
@@ -4512,11 +4390,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4534,9 +4408,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C138" t="n">
-        <v>480</v>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>节点</t>
@@ -4547,11 +4419,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4569,27 +4437,826 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>10</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>10</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
         <v>480</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>节点</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>10</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>10</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>10</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>10</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>10</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>10</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>10</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>10</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>10</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>10</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>480</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>480</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>480</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>480</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务内容表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/服务内容表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,9 @@
           <t>AI计算规划设计与实施服务（训练）</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>套</t>
@@ -475,7 +477,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -493,7 +499,9 @@
           <t>集群系统集成服务</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>套</t>
@@ -504,7 +512,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -522,7 +534,9 @@
           <t>专项/单次服务</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>次</t>
@@ -533,7 +547,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -551,7 +569,9 @@
           <t>卓悦服务</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>套</t>
@@ -562,7 +582,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -580,7 +604,9 @@
           <t>CCAE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>480</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>节点</t>
@@ -591,7 +617,11 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -609,7 +639,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>套</t>
@@ -620,7 +652,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -638,7 +674,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>套</t>
@@ -649,7 +687,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -667,7 +709,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>套</t>
@@ -678,7 +722,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -696,7 +744,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>套</t>
@@ -707,7 +757,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -725,7 +779,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>套</t>
@@ -736,7 +792,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -754,7 +814,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>套</t>
@@ -765,7 +827,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -783,7 +849,9 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>套</t>
@@ -794,7 +862,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -812,7 +884,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>套</t>
@@ -823,7 +897,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -841,7 +919,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>10</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>套</t>
@@ -852,7 +932,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -870,7 +954,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>套</t>
@@ -881,7 +967,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -899,7 +989,9 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>套</t>
@@ -910,7 +1002,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -928,7 +1024,9 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>次</t>
@@ -939,7 +1037,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -957,7 +1059,9 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>次</t>
@@ -968,7 +1072,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -986,7 +1094,9 @@
           <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>套</t>
@@ -997,7 +1107,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1015,7 +1129,9 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>480</v>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1026,7 +1142,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1044,7 +1164,9 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>480</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1055,7 +1177,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1073,7 +1199,9 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>480</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1084,7 +1212,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1102,7 +1234,9 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>480</v>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>节点</t>
@@ -1113,7 +1247,11 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -4466,9 +4604,7 @@
           <t>AI计算规划设计与实施服务（训练）</t>
         </is>
       </c>
-      <c r="C140" t="n">
-        <v>10</v>
-      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>套</t>
@@ -4479,11 +4615,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4501,9 +4633,7 @@
           <t>集群系统集成服务</t>
         </is>
       </c>
-      <c r="C141" t="n">
-        <v>10</v>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>套</t>
@@ -4514,11 +4644,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4536,9 +4662,7 @@
           <t>专项/单次服务</t>
         </is>
       </c>
-      <c r="C142" t="n">
-        <v>1</v>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>次</t>
@@ -4549,11 +4673,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4571,9 +4691,7 @@
           <t>卓悦服务</t>
         </is>
       </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>套</t>
@@ -4584,11 +4702,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4606,9 +4720,7 @@
           <t>CCAE</t>
         </is>
       </c>
-      <c r="C144" t="n">
-        <v>480</v>
-      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>节点</t>
@@ -4619,11 +4731,7 @@
           <t>L1</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4641,9 +4749,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
         </is>
       </c>
-      <c r="C145" t="n">
-        <v>10</v>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>套</t>
@@ -4654,11 +4760,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4676,9 +4778,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
         </is>
       </c>
-      <c r="C146" t="n">
-        <v>10</v>
-      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>套</t>
@@ -4689,11 +4789,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4711,9 +4807,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
         </is>
       </c>
-      <c r="C147" t="n">
-        <v>10</v>
-      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>套</t>
@@ -4724,11 +4818,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4746,9 +4836,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
         </is>
       </c>
-      <c r="C148" t="n">
-        <v>10</v>
-      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>套</t>
@@ -4759,11 +4847,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4781,9 +4865,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
         </is>
       </c>
-      <c r="C149" t="n">
-        <v>10</v>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>套</t>
@@ -4794,11 +4876,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4816,9 +4894,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
         </is>
       </c>
-      <c r="C150" t="n">
-        <v>10</v>
-      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>套</t>
@@ -4829,11 +4905,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4851,9 +4923,7 @@
           <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
         </is>
       </c>
-      <c r="C151" t="n">
-        <v>10</v>
-      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>套</t>
@@ -4864,11 +4934,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4886,9 +4952,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
         </is>
       </c>
-      <c r="C152" t="n">
-        <v>10</v>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>套</t>
@@ -4899,11 +4963,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4921,9 +4981,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
         </is>
       </c>
-      <c r="C153" t="n">
-        <v>10</v>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>套</t>
@@ -4934,11 +4992,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4956,9 +5010,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
         </is>
       </c>
-      <c r="C154" t="n">
-        <v>10</v>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>套</t>
@@ -4969,11 +5021,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4991,9 +5039,7 @@
           <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
         </is>
       </c>
-      <c r="C155" t="n">
-        <v>10</v>
-      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>套</t>
@@ -5004,11 +5050,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5026,9 +5068,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C156" t="n">
-        <v>1</v>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>次</t>
@@ -5039,11 +5079,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5061,9 +5097,7 @@
           <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
         </is>
       </c>
-      <c r="C157" t="n">
-        <v>1</v>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>次</t>
@@ -5074,11 +5108,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5096,9 +5126,7 @@
           <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
         </is>
       </c>
-      <c r="C158" t="n">
-        <v>1</v>
-      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>套</t>
@@ -5109,11 +5137,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5131,9 +5155,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
         </is>
       </c>
-      <c r="C159" t="n">
-        <v>480</v>
-      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>节点</t>
@@ -5144,11 +5166,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5166,9 +5184,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
         </is>
       </c>
-      <c r="C160" t="n">
-        <v>480</v>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>节点</t>
@@ -5179,11 +5195,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5201,9 +5213,7 @@
           <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C161" t="n">
-        <v>480</v>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>节点</t>
@@ -5214,11 +5224,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -5236,9 +5242,7 @@
           <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
         </is>
       </c>
-      <c r="C162" t="n">
-        <v>480</v>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>节点</t>
@@ -5249,14 +5253,677 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 项目管理</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜（12*Atlas 900 POD）和网络柜（4*天成灵衢交换机柜）工程安装</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点的规划设计</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点内综合布线（2688根HCCS MPO线缆-跨柜）</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 计算柜部署调试</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - HCCS网络柜部署调试</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AI计算规划设计与实施服务（训练）</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SuperPoD规划设计与实施服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - 超节点测试验证</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成规划设计</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成对接联调</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验证</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>集群系统集成服务</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>集群系统集成服务-Atlas 900 A3 SuperPoD_384卡,（1 SuperPoD，12*Atlas 900 POD+4*天成灵衢交换机柜） - AI集群系统集成验收</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>运维服务，智算，主动预防服务，液冷保障服务（&amp;gt;50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>专项/单次服务</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>运维服务，智算，主动预防服务，液冷保障服务（1-50P）； 算力：2930（P）； 服务包数量：1； 订阅时长：36个月；</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>次</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>卓悦服务</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>现场值守，服务时长为60人天，服务有效期为36个月</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CCAE-全场景互联网基础包 -计算节点管理许可-每节点</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-每节点</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CCAE-全场景互联网基础包 -计算节点管理许可-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CCAE</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CCAE-AI智算互联网高阶包(适用于Atlas 800T A3同代次产品)-3年软件订阅与保障年费-每节点(年费实际起止时间：从 " PO签订+90天 " 起算 3 年)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>节点</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
